--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.06936</v>
+        <v>17.12892</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49881</v>
+        <v>16.16642</v>
       </c>
       <c r="E2" t="n">
-        <v>16.68501</v>
+        <v>16.60336</v>
       </c>
       <c r="F2" t="n">
-        <v>41.65762</v>
+        <v>42.58918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0516</v>
+        <v>0.0518</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84669</v>
+        <v>1.84991</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.41018</v>
+        <v>16.76822</v>
       </c>
       <c r="D3" t="n">
-        <v>16.66456</v>
+        <v>16.31908</v>
       </c>
       <c r="E3" t="n">
-        <v>16.43479</v>
+        <v>16.64057</v>
       </c>
       <c r="F3" t="n">
-        <v>42.84341</v>
+        <v>41.96618</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0514</v>
+        <v>0.05069</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80747</v>
+        <v>1.87026</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.88662</v>
+      </c>
+      <c r="D4" t="n">
         <v>16.65599</v>
       </c>
-      <c r="D4" t="n">
-        <v>16.59389</v>
-      </c>
       <c r="E4" t="n">
-        <v>16.62205</v>
+        <v>16.76079</v>
       </c>
       <c r="F4" t="n">
-        <v>41.80926</v>
+        <v>42.36242</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05113</v>
+        <v>0.05048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79903</v>
+        <v>1.8305</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.66951</v>
+        <v>16.67207</v>
       </c>
       <c r="D6" t="n">
-        <v>15.92726</v>
+        <v>16.38056</v>
       </c>
       <c r="E6" t="n">
-        <v>16.50363</v>
+        <v>16.54395</v>
       </c>
       <c r="F6" t="n">
-        <v>22.11547</v>
+        <v>21.38638</v>
       </c>
       <c r="G6" t="n">
-        <v>34.88459</v>
+        <v>34.04128</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87007</v>
+        <v>16.83561</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03393</v>
+        <v>16.01858</v>
       </c>
       <c r="E7" t="n">
-        <v>16.18646</v>
+        <v>16.44452</v>
       </c>
       <c r="F7" t="n">
-        <v>21.60784</v>
+        <v>21.6144</v>
       </c>
       <c r="G7" t="n">
-        <v>34.49862</v>
+        <v>33.75402</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.51792</v>
+        <v>16.57046</v>
       </c>
       <c r="D8" t="n">
-        <v>16.01985</v>
+        <v>15.36164</v>
       </c>
       <c r="E8" t="n">
-        <v>16.09812</v>
+        <v>16.55479</v>
       </c>
       <c r="F8" t="n">
-        <v>22.11018</v>
+        <v>21.61373</v>
       </c>
       <c r="G8" t="n">
-        <v>34.2086</v>
+        <v>33.78806</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61217</v>
+        <v>0.60341</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11902</v>
+        <v>1.11366</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60477</v>
+        <v>0.62404</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10144</v>
+        <v>1.11352</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61843</v>
+        <v>0.61066</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11189</v>
+        <v>1.10035</v>
       </c>
     </row>
   </sheetData>
